--- a/templates/INFOR Precedents Template.xlsx
+++ b/templates/INFOR Precedents Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inforfg1-my.sharepoint.com/personal/twilson_inforfg_com/Documents/Desktop/Claude - INFOR/infor-workflows/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{0848B0FA-4984-42F6-80CF-A7F512337903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C0AE8AF-1B8F-4F86-A201-989A4321F926}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{0848B0FA-4984-42F6-80CF-A7F512337903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7ECAD43-D7CE-4EBD-9727-32E5ADE6B50A}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{A6BB75E0-A801-473C-9678-28D65ECCDC5E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{A6BB75E0-A801-473C-9678-28D65ECCDC5E}"/>
   </bookViews>
   <sheets>
     <sheet name="__snloffice" sheetId="2" state="veryHidden" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
   <si>
     <t>Currency</t>
   </si>
@@ -146,15 +146,6 @@
     <t>Conversion</t>
   </si>
   <si>
-    <t xml:space="preserve">TEV </t>
-  </si>
-  <si>
-    <t>/ EBITDA</t>
-  </si>
-  <si>
-    <t>/ Revenue</t>
-  </si>
-  <si>
     <t>Target Description</t>
   </si>
   <si>
@@ -164,20 +155,45 @@
     <t>Average</t>
   </si>
   <si>
-    <t>允䅁䅁䅣䅁敁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁杔䉂䑁䄰杔䉂䅁䅁杁䅁䉁䅁䅁歁䕁䅍兑䕂䕁䅣村兂䅁䅁䅁䅁䉁䅁䅁歁䕁䅍兑䕂䙁䅕睕䕂䅁䅁睁䅁䉁䄴䅁呂䙁䅁睘兂䙁䅉兓䑂䕁䅕睘䑂䕁䅷睔呂䕁䅕䅁䉁䅁䅁䅏䅁䍁䅍兓佂䙁䅙兑䵂䕁䅫䅒杁䕁䅙兖佂䕁䅍䅖䩂䕁䄸杔杁䙁䅁兑卂䕁䅅兔䙂䙁䅑兒卂䅁䅁兂䅁䉁䅑䅁歁䕁䅍兑䕂䑁䅑李睁䑁䅉睍䅁䅁䅑䅁允䅁䅁䅊䑂䕁䅅䅒䑂䕁䅅䅒䅁䅁䅙䅁䕁䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯䅁䅁䅁䅯允䅁䅁䅕䅁䅁佁㑂欵䭁䅁䅉䅁䉁䅁䅁允䅁䅁䅕乱㍔楱圲启䴸䅉䅅䅁䙁䅁䅁睁䵁䅁䅁权䝁䅁䅁权䉁䅁䅁兂䅁䅁䅁䠴浪䅑䅯杁䅁䅁䅅䅁䉁䅁䅁䅆䉁䅁䅁䅁䅁䅁杷允䅁䅁䅕䅁䑁䅁䅷䅁䭁䅁䅍䅁䭁䅁䅅䅁䙁䅁䅁䅁杄佥䅚权䍁䅁䅁允䅁䅁䅅䅁䙁䱁匱楬佇昹⽕䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯䅂䅁䅁䅯允䅁䅁䅯䄹䭣䅧䅯杁䅁䅁䅅䅁䉁䅁䅁权䙁䅁䅁</t>
+    <t>TEV / EBITDA</t>
+  </si>
+  <si>
+    <t>TEV / Revenue</t>
+  </si>
+  <si>
+    <t>NTM</t>
+  </si>
+  <si>
+    <t>LTM</t>
+  </si>
+  <si>
+    <t>LTM EBITDA</t>
+  </si>
+  <si>
+    <t>NTM Revenue</t>
+  </si>
+  <si>
+    <t>LTM Revenue</t>
+  </si>
+  <si>
+    <t>NTM EBITDA</t>
+  </si>
+  <si>
+    <t>允䅁䅁䅣䅁允䅁䅁䅊䑂䕁䅅䅒䡂䕁䅉䅕䅁䅁䅁䅁敁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁杔䉂䑁䄰杔䉂䅁䅁杁䅁䉁䄴䅁呂䙁䅁睘兂䙁䅉兓䑂䕁䅕睘䑂䕁䅷睔呂䕁䅕䅁䉁䅁䅁䅅䅁䍁䅑睑䉂䕁䅑兖呂䕁䅑䅁䑁䅁䅁䅆䅁䍁䅑睑䉂䕁䅑䅎㉁䑁䅁杍穁䅁䅁䅂䅁䑁䅧䅁橁䕁䅫杔坂䕁䅅䅔䩂䕁䅑䅉䝂䙁䅕杔䑂䙁䅑兓偂䕁䄴䅉兂䕁䅅杕䉂䕁䄰兒啂䕁䅕杕䅁䅁䅕䅁允䅁䅁䅊䑂䕁䅅䅒䑂䕁䅅䅒䅁䅁䅙䅁䍁䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯杂䅁䅁䅯允䅁䅁䅕䅁䅁佁㑂欵䭁䅁䅉䅁䉁䅁䅁允䅁䉁䅑允䅁䅁䅁䅁䵁䅉䅅䅁䙁䅁䅁睁䵁䅁䅁权䕁䅁䅁权䉁䅁䅁权い睂䅱权䍁䅁䅁允䅁䅁䅅䅁䭁䅁䅕䅁㵁</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0_);\(&quot;$&quot;#,##0.0\);&quot;--&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.0%_);\(#,##0.0%\);&quot;--&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0\x_);\(#,##0.0\x\);&quot;--&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0000000\x_);\(#,##0.0000000\x\);&quot;--&quot;"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\);&quot;--&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -224,6 +240,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Palatino Linotype"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u val="singleAccounting"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Palatino Linotype"/>
       <family val="1"/>
     </font>
@@ -356,7 +380,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -445,14 +469,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -795,7 +829,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -805,35 +839,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8293AFD-E288-4A4B-BF10-AB57948F458E}">
-  <dimension ref="B1:Y16"/>
+  <dimension ref="B1:AE16"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
-    <col min="2" max="10" width="10.7109375" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="50.7109375" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="2" max="7" width="10.7109375" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="11" width="12.42578125" style="1" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="10.7109375" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="2.7109375" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="9.5703125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="26.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" style="1" customWidth="1"/>
-    <col min="19" max="21" width="10.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="10.7109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="24" width="10.7109375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="50.7109375" style="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="50.7109375" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="10.7109375" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="2.7109375" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="9.5703125" style="1" customWidth="1"/>
+    <col min="17" max="18" width="26.140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.5703125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" style="1" customWidth="1"/>
+    <col min="21" max="25" width="10.7109375" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="29" width="13.7109375" style="1" customWidth="1"/>
+    <col min="30" max="30" width="10.7109375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="50.7109375" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="P2" s="12" t="s">
+    <row r="1" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="S2" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:31" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
@@ -861,32 +897,46 @@
         <v>3</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="11" t="s">
+      <c r="Q4" s="7"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="W4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="X4" s="11" t="s">
+      <c r="U4" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="Y4" s="11"/>
+      <c r="AE4" s="11"/>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
@@ -906,60 +956,78 @@
         <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="Q5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="R5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="S5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="R5" s="11" t="str">
-        <f>IF($Q$2="CAD", "(C$MM)", "(US$MM)")</f>
+      <c r="T5" s="11" t="str">
+        <f>IF($S$2="CAD", "(C$MM)", "(US$MM)")</f>
         <v>(C$MM)</v>
       </c>
-      <c r="S5" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="T5" s="11" t="s">
-        <v>5</v>
-      </c>
       <c r="U5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="V5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="W5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="X5" s="11" t="s">
+      <c r="Z5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Y5" s="15" t="s">
-        <v>22</v>
+      <c r="AE5" s="15" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6" spans="2:25" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:31" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B7" s="24"/>
       <c r="C7" s="5"/>
       <c r="D7" s="4"/>
@@ -970,61 +1038,79 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="14" t="str" cm="1">
-        <f t="array" ref="L7">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$Q$2&amp;$B7,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="14" t="str" cm="1">
+        <f t="array" ref="N7">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$S$2&amp;$B7,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
         <v>#PEND</v>
       </c>
-      <c r="N7" s="20">
+      <c r="P7" s="20">
         <f>+C7</f>
         <v>0</v>
       </c>
-      <c r="O7" s="21">
+      <c r="Q7" s="21">
         <f>+D7</f>
         <v>0</v>
       </c>
-      <c r="P7" s="21">
+      <c r="R7" s="21">
         <f>+E7</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="22">
+      <c r="S7" s="22">
         <f>+G7</f>
         <v>0</v>
       </c>
-      <c r="R7" s="25" t="str">
-        <f>IFERROR(L7*F7,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S7" s="25" t="str">
-        <f>IFERROR(L7*I7,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T7" s="25" t="str">
-        <f>IFERROR(L7*H7,"n/a ")</f>
+      <c r="T7" s="36" t="str">
+        <f>IFERROR(N7*F7,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U7" s="25" t="str">
-        <f>IFERROR(L7*J7,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V7" s="29" t="str">
-        <f>IFERROR($R7/S7,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="W7" s="29" t="str">
-        <f>IFERROR($R7/T7,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="X7" s="27" t="str">
-        <f>IFERROR($R7/U7,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Y7" s="23">
-        <f>+K7</f>
+        <f>IFERROR(N7*J7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V7" s="25" t="str">
+        <f>IFERROR(N7*K7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W7" s="25" t="str">
+        <f>IFERROR(N7*H7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X7" s="25" t="str">
+        <f>IFERROR(N7*I7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y7" s="25" t="str">
+        <f>IFERROR(N7*L7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z7" s="29" t="str">
+        <f>IFERROR($T7/U7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA7" s="29" t="str">
+        <f>IFERROR($T7/V7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB7" s="29" t="str">
+        <f>IFERROR($T7/W7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC7" s="29" t="str">
+        <f>IFERROR($T7/X7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD7" s="27" t="str">
+        <f>IFERROR($T7/Y7,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE7" s="23">
+        <f>+M7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B8" s="4"/>
+    <row r="8" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B8" s="24"/>
       <c r="C8" s="5"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -1034,61 +1120,79 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="14" t="str" cm="1">
-        <f t="array" ref="L8">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$Q$2&amp;$B8,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="14" t="str" cm="1">
+        <f t="array" ref="N8">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$S$2&amp;$B8,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
         <v>#PEND</v>
       </c>
-      <c r="N8" s="16">
-        <f t="shared" ref="N8:N14" si="0">+C8</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="17">
-        <f t="shared" ref="O8:O14" si="1">+D8</f>
-        <v>0</v>
-      </c>
-      <c r="P8" s="17">
-        <f t="shared" ref="P8:P14" si="2">+E8</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="18">
-        <f t="shared" ref="Q8:Q14" si="3">+G8</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="26" t="str">
-        <f t="shared" ref="R8:R14" si="4">IFERROR(L8*F8,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S8" s="26" t="str">
-        <f t="shared" ref="S8:S14" si="5">IFERROR(L8*I8,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T8" s="26" t="str">
-        <f t="shared" ref="T8:T14" si="6">IFERROR(L8*H8,"n/a ")</f>
+      <c r="P8" s="16">
+        <f t="shared" ref="P8:P14" si="0">+C8</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="17">
+        <f t="shared" ref="Q8:Q14" si="1">+D8</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="17">
+        <f t="shared" ref="R8:R14" si="2">+E8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="18">
+        <f t="shared" ref="S8:S14" si="3">+G8</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="37" t="str">
+        <f t="shared" ref="T8:T14" si="4">IFERROR(N8*F8,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U8" s="26" t="str">
-        <f t="shared" ref="U8:U14" si="7">IFERROR(L8*J8,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V8" s="30" t="str">
-        <f t="shared" ref="V8:V14" si="8">IFERROR($R8/S8,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="W8" s="30" t="str">
-        <f t="shared" ref="W8:W14" si="9">IFERROR($R8/T8,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="X8" s="28" t="str">
-        <f t="shared" ref="X8:X14" si="10">IFERROR($R8/U8,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Y8" s="19">
-        <f t="shared" ref="Y8:Y14" si="11">+K8</f>
+        <f t="shared" ref="U8:U14" si="5">IFERROR(N8*J8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V8" s="26" t="str">
+        <f t="shared" ref="V8:V14" si="6">IFERROR(N8*K8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W8" s="26" t="str">
+        <f t="shared" ref="W8:W14" si="7">IFERROR(N8*H8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X8" s="26" t="str">
+        <f t="shared" ref="X8:X14" si="8">IFERROR(N8*I8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y8" s="26" t="str">
+        <f t="shared" ref="Y8:Y14" si="9">IFERROR(N8*L8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z8" s="30" t="str">
+        <f t="shared" ref="Z8:Z14" si="10">IFERROR($T8/U8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA8" s="30" t="str">
+        <f t="shared" ref="AA8:AA14" si="11">IFERROR($T8/V8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB8" s="30" t="str">
+        <f t="shared" ref="AB8:AB14" si="12">IFERROR($T8/W8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC8" s="30" t="str">
+        <f t="shared" ref="AC8:AC14" si="13">IFERROR($T8/X8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD8" s="28" t="str">
+        <f t="shared" ref="AD8:AD14" si="14">IFERROR($T8/Y8,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE8" s="19">
+        <f t="shared" ref="AE8:AE14" si="15">+M8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B9" s="4"/>
+    <row r="9" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B9" s="24"/>
       <c r="C9" s="5"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -1098,61 +1202,79 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="14" t="str" cm="1">
-        <f t="array" ref="L9">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$Q$2&amp;$B9,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="14" t="str" cm="1">
+        <f t="array" ref="N9">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$S$2&amp;$B9,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
         <v>#PEND</v>
       </c>
-      <c r="N9" s="16">
+      <c r="P9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O9" s="17">
+      <c r="Q9" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P9" s="17">
+      <c r="R9" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="18">
+      <c r="S9" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R9" s="26" t="str">
+      <c r="T9" s="37" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="S9" s="26" t="str">
+      <c r="U9" s="26" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="T9" s="26" t="str">
+      <c r="V9" s="26" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="U9" s="26" t="str">
+      <c r="W9" s="26" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="V9" s="30" t="str">
+      <c r="X9" s="26" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="W9" s="30" t="str">
+      <c r="Y9" s="26" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="X9" s="28" t="str">
+      <c r="Z9" s="30" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="Y9" s="19">
+      <c r="AA9" s="30" t="str">
         <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB9" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC9" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD9" s="28" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE9" s="19">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B10" s="4"/>
+    <row r="10" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B10" s="24"/>
       <c r="C10" s="5"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -1162,61 +1284,79 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="14" t="str" cm="1">
-        <f t="array" ref="L10">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$Q$2&amp;$B10,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="14" t="str" cm="1">
+        <f t="array" ref="N10">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$S$2&amp;$B10,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
         <v>#PEND</v>
       </c>
-      <c r="N10" s="16">
+      <c r="P10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O10" s="17">
+      <c r="Q10" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P10" s="17">
+      <c r="R10" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="18">
+      <c r="S10" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R10" s="26" t="str">
+      <c r="T10" s="37" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="S10" s="26" t="str">
+      <c r="U10" s="26" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="T10" s="26" t="str">
+      <c r="V10" s="26" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="U10" s="26" t="str">
+      <c r="W10" s="26" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="V10" s="30" t="str">
+      <c r="X10" s="26" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="W10" s="30" t="str">
+      <c r="Y10" s="26" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="X10" s="28" t="str">
+      <c r="Z10" s="30" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="Y10" s="19">
+      <c r="AA10" s="30" t="str">
         <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB10" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC10" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD10" s="28" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE10" s="19">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B11" s="4"/>
+    <row r="11" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B11" s="24"/>
       <c r="C11" s="5"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -1226,61 +1366,79 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="14" t="str" cm="1">
-        <f t="array" ref="L11">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$Q$2&amp;$B11,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="14" t="str" cm="1">
+        <f t="array" ref="N11">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$S$2&amp;$B11,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
         <v>#PEND</v>
       </c>
-      <c r="N11" s="16">
+      <c r="P11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O11" s="17">
+      <c r="Q11" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P11" s="17">
+      <c r="R11" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="18">
+      <c r="S11" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R11" s="26" t="str">
+      <c r="T11" s="37" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="S11" s="26" t="str">
+      <c r="U11" s="26" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="T11" s="26" t="str">
+      <c r="V11" s="26" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="U11" s="26" t="str">
+      <c r="W11" s="26" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="V11" s="30" t="str">
+      <c r="X11" s="26" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="W11" s="30" t="str">
+      <c r="Y11" s="26" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="X11" s="28" t="str">
+      <c r="Z11" s="30" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="Y11" s="19">
+      <c r="AA11" s="30" t="str">
         <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB11" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC11" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD11" s="28" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE11" s="19">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B12" s="4"/>
+    <row r="12" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B12" s="24"/>
       <c r="C12" s="5"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -1290,61 +1448,79 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="14" t="str" cm="1">
-        <f t="array" ref="L12">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$Q$2&amp;$B12,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="14" t="str" cm="1">
+        <f t="array" ref="N12">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$S$2&amp;$B12,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
         <v>#PEND</v>
       </c>
-      <c r="N12" s="16">
+      <c r="P12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O12" s="17">
+      <c r="Q12" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P12" s="17">
+      <c r="R12" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="18">
+      <c r="S12" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R12" s="26" t="str">
+      <c r="T12" s="37" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="S12" s="26" t="str">
+      <c r="U12" s="26" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="T12" s="26" t="str">
+      <c r="V12" s="26" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="U12" s="26" t="str">
+      <c r="W12" s="26" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="V12" s="30" t="str">
+      <c r="X12" s="26" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="W12" s="30" t="str">
+      <c r="Y12" s="26" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="X12" s="28" t="str">
+      <c r="Z12" s="30" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="Y12" s="19">
+      <c r="AA12" s="30" t="str">
         <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB12" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC12" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD12" s="28" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE12" s="19">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B13" s="4"/>
+    <row r="13" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B13" s="24"/>
       <c r="C13" s="5"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -1354,61 +1530,79 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="14" t="str" cm="1">
-        <f t="array" ref="L13">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$Q$2&amp;$B13,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="14" t="str" cm="1">
+        <f t="array" ref="N13">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$S$2&amp;$B13,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
         <v>#PEND</v>
       </c>
-      <c r="N13" s="16">
+      <c r="P13" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O13" s="17">
+      <c r="Q13" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P13" s="17">
+      <c r="R13" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="18">
+      <c r="S13" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R13" s="26" t="str">
+      <c r="T13" s="37" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="S13" s="26" t="str">
+      <c r="U13" s="26" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="T13" s="26" t="str">
+      <c r="V13" s="26" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="U13" s="26" t="str">
+      <c r="W13" s="26" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="V13" s="30" t="str">
+      <c r="X13" s="26" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="W13" s="30" t="str">
+      <c r="Y13" s="26" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="X13" s="28" t="str">
+      <c r="Z13" s="30" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="Y13" s="19">
+      <c r="AA13" s="30" t="str">
         <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB13" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC13" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD13" s="28" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE13" s="19">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B14" s="4"/>
+    <row r="14" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B14" s="24"/>
       <c r="C14" s="5"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -1418,87 +1612,114 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="14" t="str" cm="1">
-        <f t="array" ref="L14">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$Q$2&amp;$B14,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="14" t="str" cm="1">
+        <f t="array" ref="N14">_xll.SNL.Clients.Office.Excel.Functions.SPG("$"&amp;$S$2&amp;$B14,"SP_PRICE_CLOSE",WORKDAY($C$7+1,-1),"Options: NA=NA")</f>
         <v>#PEND</v>
       </c>
-      <c r="N14" s="16">
+      <c r="P14" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O14" s="17">
+      <c r="Q14" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P14" s="17">
+      <c r="R14" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="18">
+      <c r="S14" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R14" s="26" t="str">
+      <c r="T14" s="37" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="S14" s="26" t="str">
+      <c r="U14" s="26" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="T14" s="26" t="str">
+      <c r="V14" s="26" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="U14" s="26" t="str">
+      <c r="W14" s="26" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="V14" s="30" t="str">
+      <c r="X14" s="26" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="W14" s="30" t="str">
+      <c r="Y14" s="26" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="X14" s="28" t="str">
+      <c r="Z14" s="30" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="Y14" s="19">
+      <c r="AA14" s="30" t="str">
         <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB14" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC14" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD14" s="28" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE14" s="19">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:25" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="2:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N16" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
+    <row r="15" spans="2:31" ht="3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T15" s="38"/>
+    </row>
+    <row r="16" spans="2:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P16" s="31" t="s">
+        <v>21</v>
+      </c>
       <c r="Q16" s="31"/>
-      <c r="R16" s="32" t="str">
-        <f>IFERROR(AVERAGE(R7:R14),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
-      <c r="V16" s="34" t="str">
-        <f>IFERROR(AVERAGE(V7:V14),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="W16" s="34" t="str">
-        <f>IFERROR(AVERAGE(W7:W14),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="X16" s="35" t="str">
-        <f>IFERROR(AVERAGE(X7:X14),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Y16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="33" t="str">
+        <f>IFERROR(AVERAGE(Z7:Z14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA16" s="33" t="str">
+        <f>IFERROR(AVERAGE(AA7:AA14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB16" s="33" t="str">
+        <f>IFERROR(AVERAGE(AB7:AB14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC16" s="33" t="str">
+        <f>IFERROR(AVERAGE(AC7:AC14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD16" s="34" t="str">
+        <f>IFERROR(AVERAGE(AD7:AD14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE16" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
